--- a/output/roomself_excel/5768.xlsx
+++ b/output/roomself_excel/5768.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>684530</v>
+        <v>227387</v>
       </c>
       <c r="D2" t="n">
-        <v>11036</v>
+        <v>3888</v>
       </c>
       <c r="E2" t="n">
-        <v>1123</v>
+        <v>514</v>
       </c>
       <c r="F2" t="n">
-        <v>791</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>143539</v>
+        <v>385014</v>
       </c>
       <c r="D3" t="n">
-        <v>3240</v>
+        <v>5468</v>
       </c>
       <c r="E3" t="n">
-        <v>324</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>258519</v>
+        <v>22044</v>
       </c>
       <c r="D4" t="n">
-        <v>4220</v>
+        <v>1196</v>
       </c>
       <c r="E4" t="n">
-        <v>699</v>
+        <v>132</v>
       </c>
       <c r="F4" t="n">
-        <v>417</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>175002</v>
+        <v>48792</v>
       </c>
       <c r="D5" t="n">
-        <v>5452</v>
+        <v>1960</v>
       </c>
       <c r="E5" t="n">
-        <v>260</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
-        <v>243</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48792</v>
+        <v>12730</v>
       </c>
       <c r="D6" t="n">
-        <v>1960</v>
+        <v>916</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
         <v>21</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14535</v>
+        <v>175002</v>
       </c>
       <c r="D7" t="n">
-        <v>972</v>
+        <v>5452</v>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9504</v>
+        <v>143539</v>
       </c>
       <c r="D8" t="n">
-        <v>780</v>
+        <v>3240</v>
       </c>
       <c r="E8" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5665</v>
+        <v>258519</v>
       </c>
       <c r="D9" t="n">
-        <v>632</v>
+        <v>4220</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5447</v>
+        <v>19038</v>
       </c>
       <c r="D10" t="n">
-        <v>648</v>
+        <v>1124</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12730</v>
+        <v>31047</v>
       </c>
       <c r="D11" t="n">
-        <v>916</v>
+        <v>1432</v>
       </c>
       <c r="E11" t="n">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>189150</v>
+        <v>14535</v>
       </c>
       <c r="D12" t="n">
-        <v>3540</v>
+        <v>972</v>
       </c>
       <c r="E12" t="n">
-        <v>501</v>
+        <v>131</v>
       </c>
       <c r="F12" t="n">
-        <v>113</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74448</v>
+        <v>9504</v>
       </c>
       <c r="D13" t="n">
-        <v>2380</v>
+        <v>780</v>
       </c>
       <c r="E13" t="n">
-        <v>354</v>
+        <v>124</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -734,15 +734,103 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>5665</v>
+      </c>
+      <c r="D14" t="n">
+        <v>632</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="D15" t="n">
+        <v>648</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>189150</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3540</v>
+      </c>
+      <c r="E16" t="n">
+        <v>501</v>
+      </c>
+      <c r="F16" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>74448</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2380</v>
+      </c>
+      <c r="E17" t="n">
+        <v>354</v>
+      </c>
+      <c r="F17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>3050</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D18" t="n">
         <v>551</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E18" t="n">
         <v>67</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F18" t="n">
         <v>31</v>
       </c>
     </row>

--- a/output/roomself_excel/5768.xlsx
+++ b/output/roomself_excel/5768.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>3888</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>514</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>49</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,23 @@
       <c r="D3" t="n">
         <v>5468</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>74</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>40</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +576,23 @@
       <c r="D4" t="n">
         <v>1196</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>132</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>40</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +609,23 @@
       <c r="D5" t="n">
         <v>1960</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>133</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>21</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +642,15 @@
       <c r="D6" t="n">
         <v>916</v>
       </c>
-      <c r="E6" t="n">
-        <v>53</v>
-      </c>
-      <c r="F6" t="n">
-        <v>21</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +667,38 @@
       <c r="D7" t="n">
         <v>5452</v>
       </c>
-      <c r="E7" t="n">
-        <v>260</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>243</v>
+        <v>108</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>172</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>89</v>
+      </c>
+      <c r="M7" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +716,15 @@
       <c r="D8" t="n">
         <v>3240</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +741,31 @@
       <c r="D9" t="n">
         <v>4220</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>609</v>
+      </c>
+      <c r="G9" t="n">
+        <v>49</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>168</v>
       </c>
-      <c r="F9" t="n">
+      <c r="J9" t="n">
         <v>31</v>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +782,31 @@
       <c r="D10" t="n">
         <v>1124</v>
       </c>
-      <c r="E10" t="n">
-        <v>207</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>163</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="G10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>114</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +823,23 @@
       <c r="D11" t="n">
         <v>1432</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>181</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>40</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +856,23 @@
       <c r="D12" t="n">
         <v>972</v>
       </c>
-      <c r="E12" t="n">
-        <v>131</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +889,31 @@
       <c r="D13" t="n">
         <v>780</v>
       </c>
-      <c r="E13" t="n">
-        <v>124</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G13" t="n">
+        <v>28</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>96</v>
+      </c>
+      <c r="J13" t="n">
+        <v>33</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +930,15 @@
       <c r="D14" t="n">
         <v>632</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +955,15 @@
       <c r="D15" t="n">
         <v>648</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +980,31 @@
       <c r="D16" t="n">
         <v>3540</v>
       </c>
-      <c r="E16" t="n">
-        <v>501</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>113</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G16" t="n">
+        <v>49</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>376</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1021,31 @@
       <c r="D17" t="n">
         <v>2380</v>
       </c>
-      <c r="E17" t="n">
-        <v>354</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>82</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1062,23 @@
       <c r="D18" t="n">
         <v>551</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>67</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>31</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/5768.xlsx
+++ b/output/roomself_excel/5768.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,26 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
         </is>
       </c>
     </row>
@@ -527,6 +547,10 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -560,6 +584,10 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +621,10 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -626,6 +658,10 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -651,6 +687,10 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -698,6 +738,22 @@
         <v>89</v>
       </c>
       <c r="M7" t="n">
+        <v>31</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q7" t="n">
         <v>31</v>
       </c>
     </row>
@@ -725,6 +781,10 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -766,6 +826,10 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -807,6 +871,10 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -840,6 +908,10 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -873,6 +945,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -914,6 +1002,10 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -939,6 +1031,10 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -964,6 +1060,10 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1105,22 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1046,6 +1162,10 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1079,6 +1199,10 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
